--- a/EmployeeBillableData.xlsx
+++ b/EmployeeBillableData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9400" uniqueCount="3514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9402" uniqueCount="3515">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -6215,6 +6215,9 @@
     <t>abhishek.wahane@apmosysemp.com</t>
   </si>
   <si>
+    <t>SA - AC - APM - TNM - 8765432 - DESC</t>
+  </si>
+  <si>
     <t>A-240020</t>
   </si>
   <si>
@@ -7061,7 +7064,7 @@
     <t>Priyadarshini Indira Singh</t>
   </si>
   <si>
-    <t>priyadarshini.singh@apmosysemp.com</t>
+    <t>priyadarshini.singh@apmosys.com</t>
   </si>
   <si>
     <t>A-240149</t>
@@ -29302,18 +29305,22 @@
       <c r="H638" t="s">
         <v>63</v>
       </c>
-      <c r="I638"/>
-      <c r="J638"/>
+      <c r="I638" t="s">
+        <v>2067</v>
+      </c>
+      <c r="J638" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="B639" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="C639" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="D639" t="s">
         <v>77</v>
@@ -29335,13 +29342,13 @@
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="B640" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="C640" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="D640" t="s">
         <v>77</v>
@@ -29363,13 +29370,13 @@
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B641" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="C641" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="D641" t="s">
         <v>77</v>
@@ -29391,13 +29398,13 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B642" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="C642" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="D642" t="s">
         <v>77</v>
@@ -29419,13 +29426,13 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B643" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="C643" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="D643" t="s">
         <v>13</v>
@@ -29447,13 +29454,13 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B644" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="C644" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="D644" t="s">
         <v>77</v>
@@ -29475,13 +29482,13 @@
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="B645" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="C645" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="D645" t="s">
         <v>13</v>
@@ -29503,13 +29510,13 @@
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B646" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C646" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D646" t="s">
         <v>77</v>
@@ -29531,13 +29538,13 @@
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B647" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="C647" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="D647" t="s">
         <v>77</v>
@@ -29559,13 +29566,13 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B648" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="C648" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="D648" t="s">
         <v>13</v>
@@ -29587,13 +29594,13 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B649" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="C649" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D649" t="s">
         <v>13</v>
@@ -29615,13 +29622,13 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B650" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="C650" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D650" t="s">
         <v>13</v>
@@ -29643,13 +29650,13 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B651" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="C651" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="D651" t="s">
         <v>77</v>
@@ -29671,13 +29678,13 @@
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B652" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="C652" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="D652" t="s">
         <v>77</v>
@@ -29699,13 +29706,13 @@
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="B653" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="C653" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="D653" t="s">
         <v>77</v>
@@ -29727,13 +29734,13 @@
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B654" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="C654" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="D654" t="s">
         <v>13</v>
@@ -29755,13 +29762,13 @@
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="B655" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="C655" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="D655" t="s">
         <v>77</v>
@@ -29783,13 +29790,13 @@
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B656" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="C656" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="D656" t="s">
         <v>77</v>
@@ -29811,13 +29818,13 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="B657" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="C657" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="D657" t="s">
         <v>77</v>
@@ -29839,13 +29846,13 @@
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="B658" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="C658" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="D658" t="s">
         <v>13</v>
@@ -29871,13 +29878,13 @@
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B659" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="C659" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="D659" t="s">
         <v>13</v>
@@ -29899,13 +29906,13 @@
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B660" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="C660" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="D660" t="s">
         <v>13</v>
@@ -29927,13 +29934,13 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B661" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="C661" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="D661" t="s">
         <v>77</v>
@@ -29955,13 +29962,13 @@
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B662" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="C662" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="D662" t="s">
         <v>13</v>
@@ -29983,13 +29990,13 @@
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B663" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="C663" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="D663" t="s">
         <v>13</v>
@@ -30011,13 +30018,13 @@
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B664" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="C664" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="D664" t="s">
         <v>13</v>
@@ -30039,13 +30046,13 @@
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B665" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="C665" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="D665" t="s">
         <v>13</v>
@@ -30067,13 +30074,13 @@
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B666" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C666" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="D666" t="s">
         <v>77</v>
@@ -30095,13 +30102,13 @@
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B667" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="C667" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="D667" t="s">
         <v>77</v>
@@ -30123,13 +30130,13 @@
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B668" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="C668" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="D668" t="s">
         <v>77</v>
@@ -30151,13 +30158,13 @@
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="B669" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="C669" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="D669" t="s">
         <v>13</v>
@@ -30179,13 +30186,13 @@
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="B670" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="C670" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="D670" t="s">
         <v>13</v>
@@ -30211,13 +30218,13 @@
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="B671" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="C671" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="D671" t="s">
         <v>77</v>
@@ -30239,13 +30246,13 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="B672" t="s">
         <v>1939</v>
       </c>
       <c r="C672" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="D672" t="s">
         <v>77</v>
@@ -30267,13 +30274,13 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="B673" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="C673" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="D673" t="s">
         <v>77</v>
@@ -30295,13 +30302,13 @@
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="B674" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="C674" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="D674" t="s">
         <v>77</v>
@@ -30323,13 +30330,13 @@
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B675" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C675" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="D675" t="s">
         <v>13</v>
@@ -30351,13 +30358,13 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B676" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="C676" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="D676" t="s">
         <v>13</v>
@@ -30379,13 +30386,13 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="B677" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C677" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="D677" t="s">
         <v>13</v>
@@ -30407,13 +30414,13 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="B678" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="C678" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="D678" t="s">
         <v>77</v>
@@ -30435,13 +30442,13 @@
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="B679" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C679" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="D679" t="s">
         <v>13</v>
@@ -30467,13 +30474,13 @@
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B680" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="C680" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="D680" t="s">
         <v>13</v>
@@ -30495,13 +30502,13 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B681" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="C681" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="D681" t="s">
         <v>13</v>
@@ -30527,13 +30534,13 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B682" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="C682" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="D682" t="s">
         <v>77</v>
@@ -30555,13 +30562,13 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="B683" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="C683" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="D683" t="s">
         <v>77</v>
@@ -30583,13 +30590,13 @@
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B684" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C684" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="D684" t="s">
         <v>77</v>
@@ -30611,13 +30618,13 @@
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B685" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="C685" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="D685" t="s">
         <v>13</v>
@@ -30639,13 +30646,13 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B686" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="C686" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="D686" t="s">
         <v>13</v>
@@ -30671,13 +30678,13 @@
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="B687" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="C687" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="D687" t="s">
         <v>13</v>
@@ -30699,13 +30706,13 @@
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B688" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="C688" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="D688" t="s">
         <v>13</v>
@@ -30727,13 +30734,13 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="B689" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="C689" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="D689" t="s">
         <v>13</v>
@@ -30759,13 +30766,13 @@
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="B690" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="C690" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="D690" t="s">
         <v>13</v>
@@ -30787,13 +30794,13 @@
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="B691" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="C691" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="D691" t="s">
         <v>13</v>
@@ -30815,13 +30822,13 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="B692" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="C692" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="D692" t="s">
         <v>13</v>
@@ -30843,13 +30850,13 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="B693" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="C693" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="D693" t="s">
         <v>77</v>
@@ -30871,13 +30878,13 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="B694" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="C694" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="D694" t="s">
         <v>13</v>
@@ -30899,13 +30906,13 @@
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="B695" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="C695" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="D695" t="s">
         <v>13</v>
@@ -30927,13 +30934,13 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="B696" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C696" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="D696" t="s">
         <v>77</v>
@@ -30955,13 +30962,13 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B697" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="C697" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="D697" t="s">
         <v>13</v>
@@ -30983,13 +30990,13 @@
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="B698" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C698" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="D698" t="s">
         <v>13</v>
@@ -31015,13 +31022,13 @@
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="B699" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="C699" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="D699" t="s">
         <v>77</v>
@@ -31043,13 +31050,13 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="B700" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C700" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="D700" t="s">
         <v>13</v>
@@ -31071,13 +31078,13 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="B701" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="C701" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="D701" t="s">
         <v>13</v>
@@ -31099,13 +31106,13 @@
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="B702" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="C702" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="D702" t="s">
         <v>13</v>
@@ -31127,13 +31134,13 @@
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="B703" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="C703" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="D703" t="s">
         <v>13</v>
@@ -31159,13 +31166,13 @@
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="B704" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="C704" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="D704" t="s">
         <v>13</v>
@@ -31187,13 +31194,13 @@
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="B705" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="C705" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="D705" t="s">
         <v>13</v>
@@ -31215,13 +31222,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="B706" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C706" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="D706" t="s">
         <v>77</v>
@@ -31247,13 +31254,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="B707" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="C707" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="D707" t="s">
         <v>13</v>
@@ -31275,13 +31282,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="B708" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="C708" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="D708" t="s">
         <v>13</v>
@@ -31303,13 +31310,13 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B709" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C709" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="D709" t="s">
         <v>77</v>
@@ -31331,13 +31338,13 @@
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="B710" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="C710" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="D710" t="s">
         <v>13</v>
@@ -31359,13 +31366,13 @@
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B711" t="s">
         <v>853</v>
       </c>
       <c r="C711" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="D711" t="s">
         <v>77</v>
@@ -31387,13 +31394,13 @@
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B712" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="C712" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="D712" t="s">
         <v>13</v>
@@ -31415,13 +31422,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="B713" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="C713" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="D713" t="s">
         <v>13</v>
@@ -31443,13 +31450,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="B714" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="C714" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="D714" t="s">
         <v>77</v>
@@ -31471,13 +31478,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="B715" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="C715" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="D715" t="s">
         <v>13</v>
@@ -31499,13 +31506,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="B716" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="C716" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="D716" t="s">
         <v>13</v>
@@ -31527,13 +31534,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="B717" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="C717" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="D717" t="s">
         <v>13</v>
@@ -31555,13 +31562,13 @@
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="B718" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C718" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D718" t="s">
         <v>13</v>
@@ -31583,13 +31590,13 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="B719" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="C719" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="D719" t="s">
         <v>77</v>
@@ -31611,13 +31618,13 @@
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="B720" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C720" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="D720" t="s">
         <v>13</v>
@@ -31639,13 +31646,13 @@
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="B721" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="C721" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="D721" t="s">
         <v>77</v>
@@ -31667,13 +31674,13 @@
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="B722" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="C722" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="D722" t="s">
         <v>77</v>
@@ -31695,13 +31702,13 @@
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="B723" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="C723" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="D723" t="s">
         <v>13</v>
@@ -31723,13 +31730,13 @@
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="B724" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="C724" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="D724" t="s">
         <v>13</v>
@@ -31751,13 +31758,13 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="B725" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="C725" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="D725" t="s">
         <v>13</v>
@@ -31779,13 +31786,13 @@
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="B726" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="C726" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="D726" t="s">
         <v>13</v>
@@ -31807,13 +31814,13 @@
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="B727" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="C727" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="D727" t="s">
         <v>13</v>
@@ -31839,13 +31846,13 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="B728" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="C728" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="D728" t="s">
         <v>77</v>
@@ -31867,13 +31874,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="B729" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="C729" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="D729" t="s">
         <v>77</v>
@@ -31895,13 +31902,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="B730" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="C730" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="D730" t="s">
         <v>77</v>
@@ -31923,13 +31930,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="B731" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C731" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="D731" t="s">
         <v>13</v>
@@ -31951,13 +31958,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="B732" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="C732" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D732" t="s">
         <v>13</v>
@@ -31979,13 +31986,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="B733" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="C733" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D733" t="s">
         <v>13</v>
@@ -32011,13 +32018,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="B734" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="C734" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="D734" t="s">
         <v>77</v>
@@ -32039,13 +32046,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="B735" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="C735" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="D735" t="s">
         <v>13</v>
@@ -32067,13 +32074,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="B736" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="C736" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="D736" t="s">
         <v>77</v>
@@ -32095,13 +32102,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="B737" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="C737" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="D737" t="s">
         <v>13</v>
@@ -32123,13 +32130,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="B738" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="C738" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="D738" t="s">
         <v>13</v>
@@ -32151,13 +32158,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="B739" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="C739" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="D739" t="s">
         <v>13</v>
@@ -32179,13 +32186,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="B740" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="C740" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="D740" t="s">
         <v>77</v>
@@ -32207,13 +32214,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="B741" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="C741" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="D741" t="s">
         <v>13</v>
@@ -32235,13 +32242,13 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="B742" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="C742" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="D742" t="s">
         <v>77</v>
@@ -32263,13 +32270,13 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="B743" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="C743" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D743" t="s">
         <v>13</v>
@@ -32291,13 +32298,13 @@
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="B744" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="C744" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="D744" t="s">
         <v>13</v>
@@ -32319,13 +32326,13 @@
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="B745" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="C745" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="D745" t="s">
         <v>77</v>
@@ -32347,13 +32354,13 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="B746" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="C746" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="D746" t="s">
         <v>77</v>
@@ -32375,13 +32382,13 @@
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="B747" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="C747" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="D747" t="s">
         <v>13</v>
@@ -32403,13 +32410,13 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="B748" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="C748" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="D748" t="s">
         <v>77</v>
@@ -32431,13 +32438,13 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B749" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="C749" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="D749" t="s">
         <v>77</v>
@@ -32459,13 +32466,13 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="B750" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="C750" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="D750" t="s">
         <v>13</v>
@@ -32487,13 +32494,13 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B751" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="C751" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D751" t="s">
         <v>13</v>
@@ -32519,13 +32526,13 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="B752" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="C752" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="D752" t="s">
         <v>13</v>
@@ -32547,13 +32554,13 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="B753" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C753" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D753" t="s">
         <v>13</v>
@@ -32575,13 +32582,13 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="B754" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="C754" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="D754" t="s">
         <v>13</v>
@@ -32603,13 +32610,13 @@
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="B755" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="C755" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="D755" t="s">
         <v>77</v>
@@ -32631,13 +32638,13 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="B756" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="C756" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="D756" t="s">
         <v>77</v>
@@ -32659,13 +32666,13 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B757" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="C757" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D757" t="s">
         <v>77</v>
@@ -32687,13 +32694,13 @@
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="B758" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="C758" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D758" t="s">
         <v>13</v>
@@ -32715,13 +32722,13 @@
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="B759" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="C759" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D759" t="s">
         <v>77</v>
@@ -32743,13 +32750,13 @@
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="B760" t="s">
         <v>457</v>
       </c>
       <c r="C760" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="D760" t="s">
         <v>13</v>
@@ -32771,13 +32778,13 @@
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="B761" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="C761" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D761" t="s">
         <v>13</v>
@@ -32799,13 +32806,13 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="B762" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="C762" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D762" t="s">
         <v>13</v>
@@ -32827,13 +32834,13 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="B763" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C763" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D763" t="s">
         <v>77</v>
@@ -32855,13 +32862,13 @@
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="B764" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="C764" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D764" t="s">
         <v>13</v>
@@ -32883,13 +32890,13 @@
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="B765" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="C765" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D765" t="s">
         <v>77</v>
@@ -32911,13 +32918,13 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="B766" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C766" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D766" t="s">
         <v>77</v>
@@ -32939,13 +32946,13 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="B767" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="C767" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="D767" t="s">
         <v>77</v>
@@ -32967,13 +32974,13 @@
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="B768" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="C768" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D768" t="s">
         <v>77</v>
@@ -32995,13 +33002,13 @@
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="B769" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="C769" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="D769" t="s">
         <v>13</v>
@@ -33023,13 +33030,13 @@
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="B770" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="C770" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D770" t="s">
         <v>13</v>
@@ -33051,13 +33058,13 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="B771" t="s">
         <v>437</v>
       </c>
       <c r="C771" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="D771" t="s">
         <v>77</v>
@@ -33079,13 +33086,13 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="B772" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="C772" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="D772" t="s">
         <v>13</v>
@@ -33107,13 +33114,13 @@
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="B773" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="C773" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D773" t="s">
         <v>77</v>
@@ -33135,13 +33142,13 @@
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="B774" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="C774" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="D774" t="s">
         <v>13</v>
@@ -33163,13 +33170,13 @@
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="B775" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="C775" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="D775" t="s">
         <v>13</v>
@@ -33191,13 +33198,13 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="B776" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="C776" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="D776" t="s">
         <v>13</v>
@@ -33219,13 +33226,13 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="B777" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="C777" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="D777" t="s">
         <v>13</v>
@@ -33247,13 +33254,13 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="B778" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="C778" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="D778" t="s">
         <v>13</v>
@@ -33275,13 +33282,13 @@
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="B779" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="C779" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="D779" t="s">
         <v>13</v>
@@ -33303,13 +33310,13 @@
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="B780" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="C780" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="D780" t="s">
         <v>13</v>
@@ -33331,13 +33338,13 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="B781" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C781" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="D781" t="s">
         <v>13</v>
@@ -33359,13 +33366,13 @@
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="B782" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="C782" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D782" t="s">
         <v>77</v>
@@ -33387,13 +33394,13 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="B783" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="C783" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="D783" t="s">
         <v>13</v>
@@ -33415,13 +33422,13 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B784" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="C784" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="D784" t="s">
         <v>13</v>
@@ -33443,13 +33450,13 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="B785" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="C785" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="D785" t="s">
         <v>77</v>
@@ -33471,13 +33478,13 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="B786" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="C786" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="D786" t="s">
         <v>77</v>
@@ -33499,13 +33506,13 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="B787" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="C787" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="D787" t="s">
         <v>13</v>
@@ -33527,13 +33534,13 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="B788" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="C788" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="D788" t="s">
         <v>13</v>
@@ -33555,13 +33562,13 @@
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="B789" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="C789" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="D789" t="s">
         <v>77</v>
@@ -33583,13 +33590,13 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="B790" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="C790" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="D790" t="s">
         <v>77</v>
@@ -33611,13 +33618,13 @@
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="B791" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C791" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="D791" t="s">
         <v>77</v>
@@ -33639,13 +33646,13 @@
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="B792" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="C792" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="D792" t="s">
         <v>13</v>
@@ -33667,13 +33674,13 @@
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B793" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C793" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="D793" t="s">
         <v>13</v>
@@ -33699,13 +33706,13 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="B794" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="C794" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D794" t="s">
         <v>77</v>
@@ -33727,13 +33734,13 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="B795" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="C795" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D795" t="s">
         <v>13</v>
@@ -33755,13 +33762,13 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="B796" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="C796" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="D796" t="s">
         <v>13</v>
@@ -33783,13 +33790,13 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="B797" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="C797" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="D797" t="s">
         <v>13</v>
@@ -33811,13 +33818,13 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="B798" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="C798" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="D798" t="s">
         <v>13</v>
@@ -33839,13 +33846,13 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="B799" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C799" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="D799" t="s">
         <v>13</v>
@@ -33867,13 +33874,13 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="B800" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C800" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D800" t="s">
         <v>13</v>
@@ -33895,13 +33902,13 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="B801" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="C801" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="D801" t="s">
         <v>13</v>
@@ -33923,13 +33930,13 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="B802" t="s">
         <v>305</v>
       </c>
       <c r="C802" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="D802" t="s">
         <v>13</v>
@@ -33951,13 +33958,13 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="B803" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="C803" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="D803" t="s">
         <v>77</v>
@@ -33979,13 +33986,13 @@
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="B804" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="C804" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="D804" t="s">
         <v>13</v>
@@ -34003,7 +34010,7 @@
         <v>69</v>
       </c>
       <c r="I804" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="J804" t="s">
         <v>291</v>
@@ -34011,13 +34018,13 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="B805" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="C805" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="D805" t="s">
         <v>13</v>
@@ -34039,13 +34046,13 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="B806" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="C806" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="D806" t="s">
         <v>77</v>
@@ -34067,13 +34074,13 @@
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="B807" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="C807" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="D807" t="s">
         <v>13</v>
@@ -34095,13 +34102,13 @@
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="B808" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="C808" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="D808" t="s">
         <v>77</v>
@@ -34123,13 +34130,13 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="B809" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="C809" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="D809" t="s">
         <v>13</v>
@@ -34151,13 +34158,13 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="B810" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="C810" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="D810" t="s">
         <v>77</v>
@@ -34179,13 +34186,13 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="B811" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="C811" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="D811" t="s">
         <v>13</v>
@@ -34207,13 +34214,13 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="B812" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="C812" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="D812" t="s">
         <v>77</v>
@@ -34235,13 +34242,13 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="B813" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="C813" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="D813" t="s">
         <v>77</v>
@@ -34263,13 +34270,13 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="B814" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="C814" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="D814" t="s">
         <v>77</v>
@@ -34291,13 +34298,13 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="B815" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="C815" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="D815" t="s">
         <v>13</v>
@@ -34319,13 +34326,13 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="B816" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="C816" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="D816" t="s">
         <v>77</v>
@@ -34347,13 +34354,13 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="B817" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="C817" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="D817" t="s">
         <v>13</v>
@@ -34375,13 +34382,13 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="B818" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="C818" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="D818" t="s">
         <v>77</v>
@@ -34403,13 +34410,13 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="B819" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="C819" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="D819" t="s">
         <v>77</v>
@@ -34431,13 +34438,13 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="B820" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="C820" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="D820" t="s">
         <v>13</v>
@@ -34459,13 +34466,13 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="B821" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="C821" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="D821" t="s">
         <v>77</v>
@@ -34487,13 +34494,13 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="B822" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="C822" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="D822" t="s">
         <v>77</v>
@@ -34515,13 +34522,13 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="B823" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="C823" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="D823" t="s">
         <v>77</v>
@@ -34543,13 +34550,13 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="B824" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="C824" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="D824" t="s">
         <v>77</v>
@@ -34571,13 +34578,13 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="B825" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="C825" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="D825" t="s">
         <v>13</v>
@@ -34599,13 +34606,13 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="B826" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="C826" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="D826" t="s">
         <v>77</v>
@@ -34627,13 +34634,13 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="B827" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="C827" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="D827" t="s">
         <v>77</v>
@@ -34655,13 +34662,13 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="B828" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="C828" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="D828" t="s">
         <v>77</v>
@@ -34683,13 +34690,13 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="B829" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="C829" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="D829" t="s">
         <v>77</v>
@@ -34711,13 +34718,13 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="B830" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="C830" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="D830" t="s">
         <v>13</v>
@@ -34739,13 +34746,13 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="B831" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="C831" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="D831" t="s">
         <v>13</v>
@@ -34767,13 +34774,13 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="B832" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="C832" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="D832" t="s">
         <v>77</v>
@@ -34795,13 +34802,13 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="B833" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="C833" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="D833" t="s">
         <v>77</v>
@@ -34823,13 +34830,13 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="B834" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="C834" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="D834" t="s">
         <v>77</v>
@@ -34851,13 +34858,13 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="B835" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="C835" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="D835" t="s">
         <v>13</v>
@@ -34879,13 +34886,13 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B836" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="C836" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="D836" t="s">
         <v>77</v>
@@ -34907,13 +34914,13 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="B837" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="C837" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="D837" t="s">
         <v>13</v>
@@ -34935,13 +34942,13 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="B838" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="C838" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="D838" t="s">
         <v>13</v>
@@ -34963,13 +34970,13 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="B839" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="C839" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="D839" t="s">
         <v>13</v>
@@ -34991,13 +34998,13 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="B840" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="C840" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="D840" t="s">
         <v>13</v>
@@ -35019,13 +35026,13 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="B841" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="C841" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="D841"/>
       <c r="E841" t="s">
@@ -35045,13 +35052,13 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="B842" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="C842" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="D842" t="s">
         <v>13</v>
@@ -35073,13 +35080,13 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="B843" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="C843" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="D843" t="s">
         <v>13</v>
@@ -35101,13 +35108,13 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="B844" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="C844" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="D844"/>
       <c r="E844" t="s">
@@ -35127,13 +35134,13 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="B845" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="C845" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="D845" t="s">
         <v>13</v>
@@ -35155,13 +35162,13 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="B846" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="C846" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="D846" t="s">
         <v>13</v>
@@ -35183,13 +35190,13 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="B847" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="C847" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="D847" t="s">
         <v>13</v>
@@ -35211,13 +35218,13 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="B848" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="C848" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="D848" t="s">
         <v>13</v>
@@ -35239,13 +35246,13 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="B849" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="C849" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="D849" t="s">
         <v>77</v>
@@ -35267,13 +35274,13 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="B850" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="C850" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="D850" t="s">
         <v>77</v>
@@ -35295,13 +35302,13 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="B851" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="C851" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="D851" t="s">
         <v>13</v>
@@ -35323,13 +35330,13 @@
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="B852" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="C852" t="s">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="D852" t="s">
         <v>13</v>
@@ -35351,13 +35358,13 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="B853" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="C853" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="D853" t="s">
         <v>13</v>
@@ -35379,13 +35386,13 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="B854" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="C854" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="D854" t="s">
         <v>13</v>
@@ -35407,13 +35414,13 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="B855" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="C855" t="s">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="D855" t="s">
         <v>77</v>
@@ -35435,13 +35442,13 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="B856" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="C856" t="s">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="D856" t="s">
         <v>77</v>
@@ -35463,13 +35470,13 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="B857" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="C857" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D857" t="s">
         <v>13</v>
@@ -35491,13 +35498,13 @@
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="B858" t="s">
         <v>1034</v>
       </c>
       <c r="C858" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="D858" t="s">
         <v>13</v>
@@ -35519,13 +35526,13 @@
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="B859" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="C859" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="D859" t="s">
         <v>13</v>
@@ -35547,13 +35554,13 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="B860" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="C860" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="D860" t="s">
         <v>77</v>
@@ -35575,13 +35582,13 @@
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="B861" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="C861" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="D861" t="s">
         <v>77</v>
@@ -35603,13 +35610,13 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="B862" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="C862" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="D862"/>
       <c r="E862" t="s">
@@ -35629,13 +35636,13 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="B863" t="s">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="C863" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="D863" t="s">
         <v>77</v>
@@ -35657,13 +35664,13 @@
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="B864" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="C864" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="D864" t="s">
         <v>13</v>
@@ -35689,13 +35696,13 @@
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="B865" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="C865" t="s">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="D865" t="s">
         <v>77</v>
@@ -35717,13 +35724,13 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="B866" t="s">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="C866" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="D866" t="s">
         <v>13</v>
@@ -35745,13 +35752,13 @@
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="B867" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="C867" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="D867" t="s">
         <v>13</v>
@@ -35773,13 +35780,13 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="B868" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="C868" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="D868" t="s">
         <v>13</v>
@@ -35801,13 +35808,13 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="B869" t="s">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="C869" t="s">
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="D869"/>
       <c r="E869" t="s">
@@ -35827,13 +35834,13 @@
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="B870" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="C870" t="s">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="D870" t="s">
         <v>13</v>
@@ -35855,13 +35862,13 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="B871" t="s">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="C871" t="s">
-        <v>2760</v>
+        <v>2761</v>
       </c>
       <c r="D871" t="s">
         <v>77</v>
@@ -35883,13 +35890,13 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="B872" t="s">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="C872" t="s">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="D872" t="s">
         <v>13</v>
@@ -35911,13 +35918,13 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="B873" t="s">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="C873" t="s">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="D873" t="s">
         <v>13</v>
@@ -35939,13 +35946,13 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="B874" t="s">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="C874" t="s">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="D874" t="s">
         <v>77</v>
@@ -35967,13 +35974,13 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="B875" t="s">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="C875" t="s">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="D875" t="s">
         <v>77</v>
@@ -35995,13 +36002,13 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="B876" t="s">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="C876" t="s">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="D876" t="s">
         <v>13</v>
@@ -36023,13 +36030,13 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="B877" t="s">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="C877" t="s">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D877"/>
       <c r="E877" t="s">
@@ -36049,13 +36056,13 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="B878" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="C878" t="s">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="D878" t="s">
         <v>13</v>
@@ -36077,13 +36084,13 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>2782</v>
+        <v>2783</v>
       </c>
       <c r="B879" t="s">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="C879" t="s">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="D879" t="s">
         <v>77</v>
@@ -36105,13 +36112,13 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="B880" t="s">
-        <v>2786</v>
+        <v>2787</v>
       </c>
       <c r="C880" t="s">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="D880" t="s">
         <v>13</v>
@@ -36133,13 +36140,13 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="B881" t="s">
-        <v>2789</v>
+        <v>2790</v>
       </c>
       <c r="C881" t="s">
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="D881" t="s">
         <v>13</v>
@@ -36161,13 +36168,13 @@
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>2791</v>
+        <v>2792</v>
       </c>
       <c r="B882" t="s">
-        <v>2792</v>
+        <v>2793</v>
       </c>
       <c r="C882" t="s">
-        <v>2793</v>
+        <v>2794</v>
       </c>
       <c r="D882" t="s">
         <v>13</v>
@@ -36189,13 +36196,13 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="B883" t="s">
-        <v>2795</v>
+        <v>2796</v>
       </c>
       <c r="C883" t="s">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="D883" t="s">
         <v>13</v>
@@ -36217,13 +36224,13 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="B884" t="s">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="C884" t="s">
-        <v>2799</v>
+        <v>2800</v>
       </c>
       <c r="D884"/>
       <c r="E884" t="s">
@@ -36243,13 +36250,13 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>2800</v>
+        <v>2801</v>
       </c>
       <c r="B885" t="s">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="C885" t="s">
-        <v>2802</v>
+        <v>2803</v>
       </c>
       <c r="D885" t="s">
         <v>13</v>
@@ -36271,13 +36278,13 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="B886" t="s">
-        <v>2804</v>
+        <v>2805</v>
       </c>
       <c r="C886" t="s">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="D886" t="s">
         <v>77</v>
@@ -36299,13 +36306,13 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="B887" t="s">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="C887" t="s">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="D887" t="s">
         <v>13</v>
@@ -36327,13 +36334,13 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="B888" t="s">
-        <v>2810</v>
+        <v>2811</v>
       </c>
       <c r="C888" t="s">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="D888" t="s">
         <v>13</v>
@@ -36355,13 +36362,13 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="B889" t="s">
-        <v>2813</v>
+        <v>2814</v>
       </c>
       <c r="C889" t="s">
-        <v>2814</v>
+        <v>2815</v>
       </c>
       <c r="D889" t="s">
         <v>13</v>
@@ -36387,13 +36394,13 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="B890" t="s">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="C890" t="s">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="D890" t="s">
         <v>77</v>
@@ -36415,13 +36422,13 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="B891" t="s">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="C891" t="s">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="D891" t="s">
         <v>13</v>
@@ -36443,13 +36450,13 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>2821</v>
+        <v>2822</v>
       </c>
       <c r="B892" t="s">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="C892" t="s">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="D892" t="s">
         <v>13</v>
@@ -36471,13 +36478,13 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="B893" t="s">
-        <v>2825</v>
+        <v>2826</v>
       </c>
       <c r="C893" t="s">
-        <v>2826</v>
+        <v>2827</v>
       </c>
       <c r="D893"/>
       <c r="E893" t="s">
@@ -36497,13 +36504,13 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>2827</v>
+        <v>2828</v>
       </c>
       <c r="B894" t="s">
-        <v>2828</v>
+        <v>2829</v>
       </c>
       <c r="C894" t="s">
-        <v>2829</v>
+        <v>2830</v>
       </c>
       <c r="D894" t="s">
         <v>13</v>
@@ -36525,13 +36532,13 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="B895" t="s">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c r="C895" t="s">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="D895" t="s">
         <v>13</v>
@@ -36553,13 +36560,13 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="B896" t="s">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="C896" t="s">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="D896" t="s">
         <v>77</v>
@@ -36581,13 +36588,13 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="B897" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="C897" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="D897" t="s">
         <v>77</v>
@@ -36609,13 +36616,13 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="B898" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="C898" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="D898" t="s">
         <v>77</v>
@@ -36637,13 +36644,13 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="B899" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="C899" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="D899" t="s">
         <v>77</v>
@@ -36665,13 +36672,13 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="B900" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="C900" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="D900" t="s">
         <v>13</v>
@@ -36693,13 +36700,13 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="B901" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="C901" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="D901" t="s">
         <v>77</v>
@@ -36721,13 +36728,13 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="B902" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="C902" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="D902" t="s">
         <v>13</v>
@@ -36749,13 +36756,13 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="B903" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="C903" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="D903" t="s">
         <v>77</v>
@@ -36777,13 +36784,13 @@
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="B904" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="C904" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="D904" t="s">
         <v>13</v>
@@ -36805,13 +36812,13 @@
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="B905" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="C905" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="D905" t="s">
         <v>13</v>
@@ -36833,13 +36840,13 @@
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="B906" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="C906" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="D906" t="s">
         <v>13</v>
@@ -36861,13 +36868,13 @@
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B907" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="C907" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="D907" t="s">
         <v>13</v>
@@ -36889,13 +36896,13 @@
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="B908" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="C908" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="D908" t="s">
         <v>13</v>
@@ -36917,13 +36924,13 @@
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="B909" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="C909" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="D909" t="s">
         <v>77</v>
@@ -36945,13 +36952,13 @@
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="B910" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="C910" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="D910" t="s">
         <v>77</v>
@@ -36973,13 +36980,13 @@
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="B911" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="C911" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="D911"/>
       <c r="E911" t="s">
@@ -36999,13 +37006,13 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="B912" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="C912" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="D912" t="s">
         <v>13</v>
@@ -37027,13 +37034,13 @@
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="B913" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="C913" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="D913" t="s">
         <v>77</v>
@@ -37055,13 +37062,13 @@
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="B914" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="C914" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="D914" t="s">
         <v>13</v>
@@ -37083,13 +37090,13 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="B915" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="C915" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="D915" t="s">
         <v>13</v>
@@ -37098,7 +37105,7 @@
         <v>100</v>
       </c>
       <c r="F915" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G915" t="s">
         <v>26</v>
@@ -37111,20 +37118,20 @@
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="B916" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="C916" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="D916"/>
       <c r="E916" t="s">
         <v>100</v>
       </c>
       <c r="F916" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G916" t="s">
         <v>26</v>
@@ -37137,20 +37144,20 @@
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="B917" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="C917" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="D917"/>
       <c r="E917" t="s">
         <v>100</v>
       </c>
       <c r="F917" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G917" t="s">
         <v>26</v>
@@ -37163,13 +37170,13 @@
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="B918" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="C918" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="D918" t="s">
         <v>13</v>
@@ -37191,13 +37198,13 @@
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="B919" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="C919" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="D919" t="s">
         <v>13</v>
@@ -37206,7 +37213,7 @@
         <v>100</v>
       </c>
       <c r="F919" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G919" t="s">
         <v>26</v>
@@ -37219,13 +37226,13 @@
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="B920" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="C920" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="D920" t="s">
         <v>13</v>
@@ -37251,13 +37258,13 @@
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="B921" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="C921" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="D921" t="s">
         <v>13</v>
@@ -37275,7 +37282,7 @@
         <v>75</v>
       </c>
       <c r="I921" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="J921" t="s">
         <v>21</v>
@@ -37283,13 +37290,13 @@
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B922" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="C922" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="D922" t="s">
         <v>13</v>
@@ -37307,7 +37314,7 @@
         <v>75</v>
       </c>
       <c r="I922" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="J922" t="s">
         <v>21</v>
@@ -37315,13 +37322,13 @@
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="B923" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="C923" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="D923" t="s">
         <v>13</v>
@@ -37343,13 +37350,13 @@
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B924" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="C924" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D924" t="s">
         <v>13</v>
@@ -37358,7 +37365,7 @@
         <v>100</v>
       </c>
       <c r="F924" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G924" t="s">
         <v>26</v>
@@ -37371,13 +37378,13 @@
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="B925" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="C925" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="D925" t="s">
         <v>13</v>
@@ -37386,7 +37393,7 @@
         <v>100</v>
       </c>
       <c r="F925" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G925" t="s">
         <v>26</v>
@@ -37399,13 +37406,13 @@
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B926" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C926" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="D926"/>
       <c r="E926" t="s">
@@ -37425,13 +37432,13 @@
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B927" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C927" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="D927" t="s">
         <v>13</v>
@@ -37453,13 +37460,13 @@
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="B928" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="C928" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="D928" t="s">
         <v>13</v>
@@ -37481,13 +37488,13 @@
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="B929" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="C929" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="D929" t="s">
         <v>77</v>
@@ -37509,13 +37516,13 @@
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="B930" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="C930" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="D930" t="s">
         <v>13</v>
@@ -37537,13 +37544,13 @@
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="B931" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="C931" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="D931" t="s">
         <v>13</v>
@@ -37565,13 +37572,13 @@
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="B932" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C932" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="D932" t="s">
         <v>13</v>
@@ -37593,13 +37600,13 @@
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="B933" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="C933" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="D933" t="s">
         <v>13</v>
@@ -37621,13 +37628,13 @@
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B934" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="C934" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="D934" t="s">
         <v>13</v>
@@ -37649,13 +37656,13 @@
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B935" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="C935" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="D935" t="s">
         <v>13</v>
@@ -37677,13 +37684,13 @@
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="B936" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="C936" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="D936" t="s">
         <v>13</v>
@@ -37692,7 +37699,7 @@
         <v>100</v>
       </c>
       <c r="F936" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G936" t="s">
         <v>26</v>
@@ -37705,13 +37712,13 @@
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B937" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="C937" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="D937" t="s">
         <v>13</v>
@@ -37733,13 +37740,13 @@
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="B938" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="C938" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="D938" t="s">
         <v>13</v>
@@ -37761,13 +37768,13 @@
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="B939" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="C939" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="D939" t="s">
         <v>13</v>
@@ -37789,13 +37796,13 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="B940" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="C940" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="D940" t="s">
         <v>13</v>
@@ -37817,13 +37824,13 @@
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="B941" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="C941" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="D941" t="s">
         <v>77</v>
@@ -37845,13 +37852,13 @@
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="B942" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="C942" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="D942" t="s">
         <v>13</v>
@@ -37873,13 +37880,13 @@
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="B943" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="C943" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="D943"/>
       <c r="E943" t="s">
@@ -37899,13 +37906,13 @@
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="B944" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="C944" t="s">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="D944" t="s">
         <v>13</v>
@@ -37927,13 +37934,13 @@
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="B945" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="C945" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
       <c r="D945" t="s">
         <v>13</v>
@@ -37955,13 +37962,13 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="B946" t="s">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="C946" t="s">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="D946" t="s">
         <v>13</v>
@@ -37983,13 +37990,13 @@
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="B947" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="C947" t="s">
-        <v>2990</v>
+        <v>2991</v>
       </c>
       <c r="D947" t="s">
         <v>13</v>
@@ -38011,13 +38018,13 @@
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="B948" t="s">
-        <v>2992</v>
+        <v>2993</v>
       </c>
       <c r="C948" t="s">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="D948"/>
       <c r="E948" t="s">
@@ -38037,13 +38044,13 @@
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="B949" t="s">
-        <v>2995</v>
+        <v>2996</v>
       </c>
       <c r="C949" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="D949" t="s">
         <v>13</v>
@@ -38065,13 +38072,13 @@
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="B950" t="s">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="C950" t="s">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="D950" t="s">
         <v>13</v>
@@ -38093,13 +38100,13 @@
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="B951" t="s">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="C951" t="s">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="D951" t="s">
         <v>13</v>
@@ -38121,13 +38128,13 @@
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="B952" t="s">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="C952" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="D952" t="s">
         <v>13</v>
@@ -38149,13 +38156,13 @@
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="B953" t="s">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="C953" t="s">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="D953" t="s">
         <v>13</v>
@@ -38181,13 +38188,13 @@
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="B954" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="C954" t="s">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="D954" t="s">
         <v>13</v>
@@ -38209,13 +38216,13 @@
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="B955" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="C955" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="D955" t="s">
         <v>77</v>
@@ -38237,13 +38244,13 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="B956" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="C956" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="D956" t="s">
         <v>13</v>
@@ -38265,13 +38272,13 @@
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="B957" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="C957" t="s">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="D957" t="s">
         <v>77</v>
@@ -38293,13 +38300,13 @@
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="B958" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="C958" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="D958" t="s">
         <v>13</v>
@@ -38321,13 +38328,13 @@
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="B959" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="C959" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="D959" t="s">
         <v>13</v>
@@ -38349,13 +38356,13 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="B960" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="C960" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="D960" t="s">
         <v>13</v>
@@ -38377,13 +38384,13 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="B961" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="C961" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="D961" t="s">
         <v>13</v>
@@ -38405,13 +38412,13 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="B962" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="C962" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="D962" t="s">
         <v>13</v>
@@ -38420,7 +38427,7 @@
         <v>100</v>
       </c>
       <c r="F962" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G962" t="s">
         <v>26</v>
@@ -38433,13 +38440,13 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="B963" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="C963" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="D963" t="s">
         <v>13</v>
@@ -38461,13 +38468,13 @@
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="B964" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="C964" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="D964" t="s">
         <v>13</v>
@@ -38476,7 +38483,7 @@
         <v>100</v>
       </c>
       <c r="F964" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G964" t="s">
         <v>26</v>
@@ -38489,13 +38496,13 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="B965" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="C965" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="D965" t="s">
         <v>13</v>
@@ -38504,7 +38511,7 @@
         <v>100</v>
       </c>
       <c r="F965" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G965" t="s">
         <v>26</v>
@@ -38517,13 +38524,13 @@
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="B966" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="C966" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="D966" t="s">
         <v>13</v>
@@ -38532,7 +38539,7 @@
         <v>100</v>
       </c>
       <c r="F966" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G966" t="s">
         <v>26</v>
@@ -38545,13 +38552,13 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="B967" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="C967" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="D967" t="s">
         <v>13</v>
@@ -38573,13 +38580,13 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="B968" t="s">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="C968" t="s">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="D968" t="s">
         <v>13</v>
@@ -38588,7 +38595,7 @@
         <v>100</v>
       </c>
       <c r="F968" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G968" t="s">
         <v>26</v>
@@ -38601,13 +38608,13 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="B969" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C969" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="D969" t="s">
         <v>13</v>
@@ -38616,7 +38623,7 @@
         <v>100</v>
       </c>
       <c r="F969" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G969" t="s">
         <v>26</v>
@@ -38629,13 +38636,13 @@
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="B970" t="s">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C970" t="s">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="D970" t="s">
         <v>13</v>
@@ -38644,7 +38651,7 @@
         <v>100</v>
       </c>
       <c r="F970" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G970" t="s">
         <v>26</v>
@@ -38657,13 +38664,13 @@
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="B971" t="s">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C971" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D971" t="s">
         <v>13</v>
@@ -38685,13 +38692,13 @@
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="B972" t="s">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C972" t="s">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="D972" t="s">
         <v>13</v>
@@ -38700,7 +38707,7 @@
         <v>100</v>
       </c>
       <c r="F972" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G972" t="s">
         <v>26</v>
@@ -38713,13 +38720,13 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="B973" t="s">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C973" t="s">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="D973" t="s">
         <v>13</v>
@@ -38728,7 +38735,7 @@
         <v>100</v>
       </c>
       <c r="F973" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G973" t="s">
         <v>26</v>
@@ -38741,13 +38748,13 @@
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="B974" t="s">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C974" t="s">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="D974" t="s">
         <v>13</v>
@@ -38756,7 +38763,7 @@
         <v>100</v>
       </c>
       <c r="F974" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G974" t="s">
         <v>26</v>
@@ -38769,13 +38776,13 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="B975" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="C975" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="D975" t="s">
         <v>13</v>
@@ -38784,7 +38791,7 @@
         <v>100</v>
       </c>
       <c r="F975" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G975" t="s">
         <v>26</v>
@@ -38797,13 +38804,13 @@
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="B976" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="C976" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="D976" t="s">
         <v>13</v>
@@ -38825,13 +38832,13 @@
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="B977" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="C977" t="s">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="D977" t="s">
         <v>13</v>
@@ -38840,7 +38847,7 @@
         <v>100</v>
       </c>
       <c r="F977" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G977" t="s">
         <v>26</v>
@@ -38853,13 +38860,13 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="B978" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="C978" t="s">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="D978" t="s">
         <v>13</v>
@@ -38868,7 +38875,7 @@
         <v>100</v>
       </c>
       <c r="F978" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G978" t="s">
         <v>26</v>
@@ -38881,13 +38888,13 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="B979" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="C979" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="D979" t="s">
         <v>13</v>
@@ -38909,13 +38916,13 @@
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="B980" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="C980" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="D980" t="s">
         <v>13</v>
@@ -38924,7 +38931,7 @@
         <v>100</v>
       </c>
       <c r="F980" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G980" t="s">
         <v>26</v>
@@ -38937,13 +38944,13 @@
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="B981" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="C981" t="s">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="D981" t="s">
         <v>13</v>
@@ -38952,7 +38959,7 @@
         <v>100</v>
       </c>
       <c r="F981" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G981" t="s">
         <v>26</v>
@@ -38965,13 +38972,13 @@
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="B982" t="s">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="C982" t="s">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="D982" t="s">
         <v>13</v>
@@ -38980,7 +38987,7 @@
         <v>100</v>
       </c>
       <c r="F982" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G982" t="s">
         <v>26</v>
@@ -38993,13 +39000,13 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="B983" t="s">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="C983" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="D983" t="s">
         <v>13</v>
@@ -39021,13 +39028,13 @@
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="B984" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="C984" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="D984" t="s">
         <v>13</v>
@@ -39036,7 +39043,7 @@
         <v>100</v>
       </c>
       <c r="F984" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G984" t="s">
         <v>26</v>
@@ -39049,13 +39056,13 @@
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="B985" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="C985" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="D985" t="s">
         <v>13</v>
@@ -39064,7 +39071,7 @@
         <v>100</v>
       </c>
       <c r="F985" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G985" t="s">
         <v>26</v>
@@ -39077,13 +39084,13 @@
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="B986" t="s">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="C986" t="s">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="D986" t="s">
         <v>13</v>
@@ -39092,7 +39099,7 @@
         <v>100</v>
       </c>
       <c r="F986" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G986" t="s">
         <v>26</v>
@@ -39105,13 +39112,13 @@
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="B987" t="s">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="C987" t="s">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="D987" t="s">
         <v>13</v>
@@ -39120,7 +39127,7 @@
         <v>100</v>
       </c>
       <c r="F987" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G987" t="s">
         <v>26</v>
@@ -39133,13 +39140,13 @@
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="B988" t="s">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="C988" t="s">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="D988" t="s">
         <v>13</v>
@@ -39148,7 +39155,7 @@
         <v>100</v>
       </c>
       <c r="F988" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G988" t="s">
         <v>26</v>
@@ -39161,13 +39168,13 @@
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="B989" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="C989" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="D989" t="s">
         <v>13</v>
@@ -39176,7 +39183,7 @@
         <v>100</v>
       </c>
       <c r="F989" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G989" t="s">
         <v>26</v>
@@ -39189,13 +39196,13 @@
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="B990" t="s">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="C990" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="D990" t="s">
         <v>13</v>
@@ -39204,7 +39211,7 @@
         <v>100</v>
       </c>
       <c r="F990" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G990" t="s">
         <v>26</v>
@@ -39217,13 +39224,13 @@
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="B991" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="C991" t="s">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="D991" t="s">
         <v>13</v>
@@ -39232,7 +39239,7 @@
         <v>100</v>
       </c>
       <c r="F991" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G991" t="s">
         <v>26</v>
@@ -39245,13 +39252,13 @@
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="B992" t="s">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="C992" t="s">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="D992" t="s">
         <v>13</v>
@@ -39273,13 +39280,13 @@
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="B993" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="C993" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="D993" t="s">
         <v>13</v>
@@ -39301,13 +39308,13 @@
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="B994" t="s">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="C994" t="s">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="D994" t="s">
         <v>13</v>
@@ -39316,7 +39323,7 @@
         <v>100</v>
       </c>
       <c r="F994" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G994" t="s">
         <v>26</v>
@@ -39329,13 +39336,13 @@
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="B995" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="C995" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="D995" t="s">
         <v>13</v>
@@ -39344,7 +39351,7 @@
         <v>100</v>
       </c>
       <c r="F995" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G995" t="s">
         <v>26</v>
@@ -39357,13 +39364,13 @@
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="B996" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="C996" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="D996" t="s">
         <v>13</v>
@@ -39385,13 +39392,13 @@
     </row>
     <row r="997">
       <c r="A997" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="B997" t="s">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="C997" t="s">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="D997" t="s">
         <v>13</v>
@@ -39400,7 +39407,7 @@
         <v>100</v>
       </c>
       <c r="F997" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G997" t="s">
         <v>26</v>
@@ -39413,13 +39420,13 @@
     </row>
     <row r="998">
       <c r="A998" t="s">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="B998" t="s">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="C998" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="D998" t="s">
         <v>13</v>
@@ -39428,7 +39435,7 @@
         <v>100</v>
       </c>
       <c r="F998" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G998" t="s">
         <v>26</v>
@@ -39441,13 +39448,13 @@
     </row>
     <row r="999">
       <c r="A999" t="s">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="B999" t="s">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="C999" t="s">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="D999" t="s">
         <v>13</v>
@@ -39456,7 +39463,7 @@
         <v>100</v>
       </c>
       <c r="F999" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G999" t="s">
         <v>26</v>
@@ -39469,13 +39476,13 @@
     </row>
     <row r="1000">
       <c r="A1000" t="s">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="B1000" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="C1000" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="D1000" t="s">
         <v>13</v>
@@ -39497,13 +39504,13 @@
     </row>
     <row r="1001">
       <c r="A1001" t="s">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="B1001" t="s">
         <v>239</v>
       </c>
       <c r="C1001" t="s">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="D1001" t="s">
         <v>13</v>
@@ -39525,13 +39532,13 @@
     </row>
     <row r="1002">
       <c r="A1002" t="s">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="B1002" t="s">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="C1002" t="s">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="D1002" t="s">
         <v>13</v>
@@ -39553,13 +39560,13 @@
     </row>
     <row r="1003">
       <c r="A1003" t="s">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="B1003" t="s">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="C1003" t="s">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="D1003" t="s">
         <v>13</v>
@@ -39581,13 +39588,13 @@
     </row>
     <row r="1004">
       <c r="A1004" t="s">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="B1004" t="s">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="C1004" t="s">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="D1004" t="s">
         <v>13</v>
@@ -39609,13 +39616,13 @@
     </row>
     <row r="1005">
       <c r="A1005" t="s">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="B1005" t="s">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="C1005" t="s">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="D1005" t="s">
         <v>77</v>
@@ -39637,13 +39644,13 @@
     </row>
     <row r="1006">
       <c r="A1006" t="s">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="B1006" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="C1006" t="s">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="D1006" t="s">
         <v>13</v>
@@ -39665,13 +39672,13 @@
     </row>
     <row r="1007">
       <c r="A1007" t="s">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="B1007" t="s">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="C1007" t="s">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="D1007" t="s">
         <v>13</v>
@@ -39693,13 +39700,13 @@
     </row>
     <row r="1008">
       <c r="A1008" t="s">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="B1008" t="s">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="C1008" t="s">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="D1008" t="s">
         <v>13</v>
@@ -39708,7 +39715,7 @@
         <v>100</v>
       </c>
       <c r="F1008" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1008" t="s">
         <v>26</v>
@@ -39721,13 +39728,13 @@
     </row>
     <row r="1009">
       <c r="A1009" t="s">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="B1009" t="s">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="C1009" t="s">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="D1009" t="s">
         <v>13</v>
@@ -39749,13 +39756,13 @@
     </row>
     <row r="1010">
       <c r="A1010" t="s">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="B1010" t="s">
         <v>298</v>
       </c>
       <c r="C1010" t="s">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="D1010" t="s">
         <v>13</v>
@@ -39777,13 +39784,13 @@
     </row>
     <row r="1011">
       <c r="A1011" t="s">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="B1011" t="s">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="C1011" t="s">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="D1011" t="s">
         <v>13</v>
@@ -39805,13 +39812,13 @@
     </row>
     <row r="1012">
       <c r="A1012" t="s">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="B1012" t="s">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="C1012" t="s">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="D1012" t="s">
         <v>13</v>
@@ -39833,13 +39840,13 @@
     </row>
     <row r="1013">
       <c r="A1013" t="s">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="B1013" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="C1013" t="s">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="D1013" t="s">
         <v>13</v>
@@ -39861,13 +39868,13 @@
     </row>
     <row r="1014">
       <c r="A1014" t="s">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="B1014" t="s">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="C1014" t="s">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="D1014" t="s">
         <v>77</v>
@@ -39889,13 +39896,13 @@
     </row>
     <row r="1015">
       <c r="A1015" t="s">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="B1015" t="s">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="C1015" t="s">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="D1015" t="s">
         <v>13</v>
@@ -39917,13 +39924,13 @@
     </row>
     <row r="1016">
       <c r="A1016" t="s">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="B1016" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="C1016" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="D1016" t="s">
         <v>13</v>
@@ -39945,13 +39952,13 @@
     </row>
     <row r="1017">
       <c r="A1017" t="s">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="B1017" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="C1017" t="s">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="D1017" t="s">
         <v>13</v>
@@ -39973,13 +39980,13 @@
     </row>
     <row r="1018">
       <c r="A1018" t="s">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="B1018" t="s">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="C1018" t="s">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="D1018" t="s">
         <v>13</v>
@@ -40001,13 +40008,13 @@
     </row>
     <row r="1019">
       <c r="A1019" t="s">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="B1019" t="s">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="C1019" t="s">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="D1019" t="s">
         <v>13</v>
@@ -40029,13 +40036,13 @@
     </row>
     <row r="1020">
       <c r="A1020" t="s">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="B1020" t="s">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="C1020" t="s">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="D1020" t="s">
         <v>13</v>
@@ -40044,7 +40051,7 @@
         <v>100</v>
       </c>
       <c r="F1020" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1020" t="s">
         <v>26</v>
@@ -40057,13 +40064,13 @@
     </row>
     <row r="1021">
       <c r="A1021" t="s">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="B1021" t="s">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="C1021" t="s">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="D1021" t="s">
         <v>13</v>
@@ -40085,13 +40092,13 @@
     </row>
     <row r="1022">
       <c r="A1022" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="B1022" t="s">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="C1022" t="s">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="D1022" t="s">
         <v>13</v>
@@ -40113,13 +40120,13 @@
     </row>
     <row r="1023">
       <c r="A1023" t="s">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="B1023" t="s">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="C1023" t="s">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="D1023" t="s">
         <v>13</v>
@@ -40141,13 +40148,13 @@
     </row>
     <row r="1024">
       <c r="A1024" t="s">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="B1024" t="s">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="C1024" t="s">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="D1024" t="s">
         <v>13</v>
@@ -40169,13 +40176,13 @@
     </row>
     <row r="1025">
       <c r="A1025" t="s">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="B1025" t="s">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="C1025" t="s">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="D1025" t="s">
         <v>13</v>
@@ -40184,7 +40191,7 @@
         <v>100</v>
       </c>
       <c r="F1025" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1025" t="s">
         <v>26</v>
@@ -40197,13 +40204,13 @@
     </row>
     <row r="1026">
       <c r="A1026" t="s">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="B1026" t="s">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="C1026" t="s">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="D1026" t="s">
         <v>13</v>
@@ -40212,7 +40219,7 @@
         <v>100</v>
       </c>
       <c r="F1026" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1026" t="s">
         <v>26</v>
@@ -40225,13 +40232,13 @@
     </row>
     <row r="1027">
       <c r="A1027" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="B1027" t="s">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="C1027" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="D1027" t="s">
         <v>13</v>
@@ -40240,7 +40247,7 @@
         <v>100</v>
       </c>
       <c r="F1027" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1027" t="s">
         <v>26</v>
@@ -40253,13 +40260,13 @@
     </row>
     <row r="1028">
       <c r="A1028" t="s">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="B1028" t="s">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="C1028" t="s">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="D1028" t="s">
         <v>13</v>
@@ -40268,7 +40275,7 @@
         <v>100</v>
       </c>
       <c r="F1028" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1028" t="s">
         <v>26</v>
@@ -40281,13 +40288,13 @@
     </row>
     <row r="1029">
       <c r="A1029" t="s">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="B1029" t="s">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="C1029" t="s">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="D1029" t="s">
         <v>13</v>
@@ -40296,7 +40303,7 @@
         <v>100</v>
       </c>
       <c r="F1029" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1029" t="s">
         <v>26</v>
@@ -40309,13 +40316,13 @@
     </row>
     <row r="1030">
       <c r="A1030" t="s">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="B1030" t="s">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="C1030" t="s">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="D1030" t="s">
         <v>13</v>
@@ -40324,7 +40331,7 @@
         <v>100</v>
       </c>
       <c r="F1030" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1030" t="s">
         <v>26</v>
@@ -40337,13 +40344,13 @@
     </row>
     <row r="1031">
       <c r="A1031" t="s">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="B1031" t="s">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="C1031" t="s">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="D1031" t="s">
         <v>13</v>
@@ -40352,7 +40359,7 @@
         <v>100</v>
       </c>
       <c r="F1031" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1031" t="s">
         <v>26</v>
@@ -40365,13 +40372,13 @@
     </row>
     <row r="1032">
       <c r="A1032" t="s">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="B1032" t="s">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="C1032" t="s">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="D1032" t="s">
         <v>13</v>
@@ -40380,7 +40387,7 @@
         <v>100</v>
       </c>
       <c r="F1032" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1032" t="s">
         <v>26</v>
@@ -40393,13 +40400,13 @@
     </row>
     <row r="1033">
       <c r="A1033" t="s">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="B1033" t="s">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="C1033" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="D1033" t="s">
         <v>13</v>
@@ -40408,7 +40415,7 @@
         <v>100</v>
       </c>
       <c r="F1033" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1033" t="s">
         <v>26</v>
@@ -40421,13 +40428,13 @@
     </row>
     <row r="1034">
       <c r="A1034" t="s">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="B1034" t="s">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="C1034" t="s">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="D1034" t="s">
         <v>13</v>
@@ -40436,7 +40443,7 @@
         <v>100</v>
       </c>
       <c r="F1034" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1034" t="s">
         <v>26</v>
@@ -40449,13 +40456,13 @@
     </row>
     <row r="1035">
       <c r="A1035" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="B1035" t="s">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="C1035" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="D1035" t="s">
         <v>13</v>
@@ -40464,7 +40471,7 @@
         <v>100</v>
       </c>
       <c r="F1035" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1035" t="s">
         <v>26</v>
@@ -40477,13 +40484,13 @@
     </row>
     <row r="1036">
       <c r="A1036" t="s">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="B1036" t="s">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="C1036" t="s">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="D1036" t="s">
         <v>13</v>
@@ -40492,7 +40499,7 @@
         <v>100</v>
       </c>
       <c r="F1036" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1036" t="s">
         <v>26</v>
@@ -40505,13 +40512,13 @@
     </row>
     <row r="1037">
       <c r="A1037" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="B1037" t="s">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="C1037" t="s">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="D1037" t="s">
         <v>13</v>
@@ -40520,7 +40527,7 @@
         <v>100</v>
       </c>
       <c r="F1037" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1037" t="s">
         <v>26</v>
@@ -40533,13 +40540,13 @@
     </row>
     <row r="1038">
       <c r="A1038" t="s">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="B1038" t="s">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="C1038" t="s">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="D1038" t="s">
         <v>13</v>
@@ -40548,7 +40555,7 @@
         <v>100</v>
       </c>
       <c r="F1038" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1038" t="s">
         <v>26</v>
@@ -40561,13 +40568,13 @@
     </row>
     <row r="1039">
       <c r="A1039" t="s">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="B1039" t="s">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="C1039" t="s">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="D1039" t="s">
         <v>13</v>
@@ -40576,7 +40583,7 @@
         <v>100</v>
       </c>
       <c r="F1039" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1039" t="s">
         <v>26</v>
@@ -40589,13 +40596,13 @@
     </row>
     <row r="1040">
       <c r="A1040" t="s">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="B1040" t="s">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="C1040" t="s">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="D1040" t="s">
         <v>13</v>
@@ -40604,7 +40611,7 @@
         <v>100</v>
       </c>
       <c r="F1040" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1040" t="s">
         <v>26</v>
@@ -40617,13 +40624,13 @@
     </row>
     <row r="1041">
       <c r="A1041" t="s">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="B1041" t="s">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="C1041" t="s">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="D1041" t="s">
         <v>13</v>
@@ -40632,7 +40639,7 @@
         <v>100</v>
       </c>
       <c r="F1041" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1041" t="s">
         <v>26</v>
@@ -40645,13 +40652,13 @@
     </row>
     <row r="1042">
       <c r="A1042" t="s">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="B1042" t="s">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="C1042" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="D1042" t="s">
         <v>13</v>
@@ -40660,7 +40667,7 @@
         <v>100</v>
       </c>
       <c r="F1042" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1042" t="s">
         <v>26</v>
@@ -40673,13 +40680,13 @@
     </row>
     <row r="1043">
       <c r="A1043" t="s">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="B1043" t="s">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="C1043" t="s">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="D1043" t="s">
         <v>13</v>
@@ -40688,7 +40695,7 @@
         <v>100</v>
       </c>
       <c r="F1043" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1043" t="s">
         <v>26</v>
@@ -40701,13 +40708,13 @@
     </row>
     <row r="1044">
       <c r="A1044" t="s">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="B1044" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="C1044" t="s">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="D1044" t="s">
         <v>13</v>
@@ -40716,7 +40723,7 @@
         <v>100</v>
       </c>
       <c r="F1044" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1044" t="s">
         <v>26</v>
@@ -40729,13 +40736,13 @@
     </row>
     <row r="1045">
       <c r="A1045" t="s">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="B1045" t="s">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="C1045" t="s">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="D1045" t="s">
         <v>13</v>
@@ -40744,7 +40751,7 @@
         <v>100</v>
       </c>
       <c r="F1045" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1045" t="s">
         <v>26</v>
@@ -40757,13 +40764,13 @@
     </row>
     <row r="1046">
       <c r="A1046" t="s">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="B1046" t="s">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="C1046" t="s">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="D1046" t="s">
         <v>13</v>
@@ -40772,7 +40779,7 @@
         <v>100</v>
       </c>
       <c r="F1046" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1046" t="s">
         <v>26</v>
@@ -40785,13 +40792,13 @@
     </row>
     <row r="1047">
       <c r="A1047" t="s">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="B1047" t="s">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="C1047" t="s">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="D1047" t="s">
         <v>13</v>
@@ -40800,7 +40807,7 @@
         <v>100</v>
       </c>
       <c r="F1047" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1047" t="s">
         <v>26</v>
@@ -40813,13 +40820,13 @@
     </row>
     <row r="1048">
       <c r="A1048" t="s">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="B1048" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="C1048" t="s">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="D1048" t="s">
         <v>13</v>
@@ -40828,7 +40835,7 @@
         <v>100</v>
       </c>
       <c r="F1048" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1048" t="s">
         <v>26</v>
@@ -40841,13 +40848,13 @@
     </row>
     <row r="1049">
       <c r="A1049" t="s">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="B1049" t="s">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="C1049" t="s">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="D1049" t="s">
         <v>13</v>
@@ -40856,7 +40863,7 @@
         <v>100</v>
       </c>
       <c r="F1049" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1049" t="s">
         <v>26</v>
@@ -40869,13 +40876,13 @@
     </row>
     <row r="1050">
       <c r="A1050" t="s">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="B1050" t="s">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="C1050" t="s">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="D1050" t="s">
         <v>13</v>
@@ -40884,7 +40891,7 @@
         <v>100</v>
       </c>
       <c r="F1050" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1050" t="s">
         <v>26</v>
@@ -40897,13 +40904,13 @@
     </row>
     <row r="1051">
       <c r="A1051" t="s">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="B1051" t="s">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="C1051" t="s">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="D1051" t="s">
         <v>13</v>
@@ -40912,7 +40919,7 @@
         <v>100</v>
       </c>
       <c r="F1051" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1051" t="s">
         <v>26</v>
@@ -40925,13 +40932,13 @@
     </row>
     <row r="1052">
       <c r="A1052" t="s">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="B1052" t="s">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="C1052" t="s">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="D1052" t="s">
         <v>13</v>
@@ -40940,7 +40947,7 @@
         <v>100</v>
       </c>
       <c r="F1052" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1052" t="s">
         <v>26</v>
@@ -40953,13 +40960,13 @@
     </row>
     <row r="1053">
       <c r="A1053" t="s">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="B1053" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="C1053" t="s">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="D1053" t="s">
         <v>13</v>
@@ -40968,7 +40975,7 @@
         <v>100</v>
       </c>
       <c r="F1053" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1053" t="s">
         <v>26</v>
@@ -40981,13 +40988,13 @@
     </row>
     <row r="1054">
       <c r="A1054" t="s">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="B1054" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="C1054" t="s">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="D1054" t="s">
         <v>13</v>
@@ -40996,7 +41003,7 @@
         <v>100</v>
       </c>
       <c r="F1054" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1054" t="s">
         <v>26</v>
@@ -41009,13 +41016,13 @@
     </row>
     <row r="1055">
       <c r="A1055" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="B1055" t="s">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="C1055" t="s">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="D1055" t="s">
         <v>13</v>
@@ -41024,7 +41031,7 @@
         <v>100</v>
       </c>
       <c r="F1055" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1055" t="s">
         <v>26</v>
@@ -41037,13 +41044,13 @@
     </row>
     <row r="1056">
       <c r="A1056" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="B1056" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="C1056" t="s">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="D1056" t="s">
         <v>13</v>
@@ -41052,7 +41059,7 @@
         <v>100</v>
       </c>
       <c r="F1056" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1056" t="s">
         <v>26</v>
@@ -41065,13 +41072,13 @@
     </row>
     <row r="1057">
       <c r="A1057" t="s">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="B1057" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="C1057" t="s">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="D1057" t="s">
         <v>13</v>
@@ -41080,7 +41087,7 @@
         <v>100</v>
       </c>
       <c r="F1057" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1057" t="s">
         <v>26</v>
@@ -41093,13 +41100,13 @@
     </row>
     <row r="1058">
       <c r="A1058" t="s">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="B1058" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="C1058" t="s">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="D1058" t="s">
         <v>13</v>
@@ -41108,7 +41115,7 @@
         <v>100</v>
       </c>
       <c r="F1058" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1058" t="s">
         <v>26</v>
@@ -41121,13 +41128,13 @@
     </row>
     <row r="1059">
       <c r="A1059" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="B1059" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="C1059" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="D1059" t="s">
         <v>13</v>
@@ -41136,7 +41143,7 @@
         <v>100</v>
       </c>
       <c r="F1059" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1059" t="s">
         <v>26</v>
@@ -41149,13 +41156,13 @@
     </row>
     <row r="1060">
       <c r="A1060" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="B1060" t="s">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="C1060" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="D1060" t="s">
         <v>13</v>
@@ -41164,7 +41171,7 @@
         <v>100</v>
       </c>
       <c r="F1060" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1060" t="s">
         <v>26</v>
@@ -41177,13 +41184,13 @@
     </row>
     <row r="1061">
       <c r="A1061" t="s">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="B1061" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="C1061" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="D1061" t="s">
         <v>13</v>
@@ -41192,7 +41199,7 @@
         <v>100</v>
       </c>
       <c r="F1061" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1061" t="s">
         <v>26</v>
@@ -41205,13 +41212,13 @@
     </row>
     <row r="1062">
       <c r="A1062" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="B1062" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="C1062" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="D1062" t="s">
         <v>13</v>
@@ -41220,7 +41227,7 @@
         <v>100</v>
       </c>
       <c r="F1062" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1062" t="s">
         <v>26</v>
@@ -41233,13 +41240,13 @@
     </row>
     <row r="1063">
       <c r="A1063" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="B1063" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="C1063" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="D1063" t="s">
         <v>13</v>
@@ -41248,7 +41255,7 @@
         <v>100</v>
       </c>
       <c r="F1063" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1063" t="s">
         <v>26</v>
@@ -41261,13 +41268,13 @@
     </row>
     <row r="1064">
       <c r="A1064" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="B1064" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="C1064" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="D1064" t="s">
         <v>13</v>
@@ -41276,7 +41283,7 @@
         <v>100</v>
       </c>
       <c r="F1064" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1064" t="s">
         <v>26</v>
@@ -41289,13 +41296,13 @@
     </row>
     <row r="1065">
       <c r="A1065" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="B1065" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="C1065" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="D1065" t="s">
         <v>13</v>
@@ -41304,7 +41311,7 @@
         <v>100</v>
       </c>
       <c r="F1065" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1065" t="s">
         <v>26</v>
@@ -41317,13 +41324,13 @@
     </row>
     <row r="1066">
       <c r="A1066" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="B1066" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="C1066" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="D1066" t="s">
         <v>13</v>
@@ -41332,7 +41339,7 @@
         <v>100</v>
       </c>
       <c r="F1066" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1066" t="s">
         <v>26</v>
@@ -41345,13 +41352,13 @@
     </row>
     <row r="1067">
       <c r="A1067" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="B1067" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="C1067" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="D1067" t="s">
         <v>13</v>
@@ -41360,7 +41367,7 @@
         <v>100</v>
       </c>
       <c r="F1067" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1067" t="s">
         <v>26</v>
@@ -41373,13 +41380,13 @@
     </row>
     <row r="1068">
       <c r="A1068" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="B1068" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="C1068" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="D1068" t="s">
         <v>13</v>
@@ -41388,7 +41395,7 @@
         <v>100</v>
       </c>
       <c r="F1068" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1068" t="s">
         <v>26</v>
@@ -41401,13 +41408,13 @@
     </row>
     <row r="1069">
       <c r="A1069" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="B1069" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="C1069" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="D1069" t="s">
         <v>13</v>
@@ -41416,7 +41423,7 @@
         <v>100</v>
       </c>
       <c r="F1069" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1069" t="s">
         <v>26</v>
@@ -41429,13 +41436,13 @@
     </row>
     <row r="1070">
       <c r="A1070" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="B1070" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="C1070" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="D1070" t="s">
         <v>13</v>
@@ -41444,7 +41451,7 @@
         <v>100</v>
       </c>
       <c r="F1070" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1070" t="s">
         <v>26</v>
@@ -41457,13 +41464,13 @@
     </row>
     <row r="1071">
       <c r="A1071" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="B1071" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="C1071" t="s">
-        <v>3359</v>
+        <v>3360</v>
       </c>
       <c r="D1071" t="s">
         <v>13</v>
@@ -41485,13 +41492,13 @@
     </row>
     <row r="1072">
       <c r="A1072" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="B1072" t="s">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="C1072" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="D1072" t="s">
         <v>13</v>
@@ -41513,13 +41520,13 @@
     </row>
     <row r="1073">
       <c r="A1073" t="s">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="B1073" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="C1073" t="s">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="D1073" t="s">
         <v>13</v>
@@ -41541,13 +41548,13 @@
     </row>
     <row r="1074">
       <c r="A1074" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="B1074" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="C1074" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="D1074" t="s">
         <v>13</v>
@@ -41569,13 +41576,13 @@
     </row>
     <row r="1075">
       <c r="A1075" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="B1075" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="C1075" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="D1075" t="s">
         <v>13</v>
@@ -41584,7 +41591,7 @@
         <v>100</v>
       </c>
       <c r="F1075" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1075" t="s">
         <v>26</v>
@@ -41597,13 +41604,13 @@
     </row>
     <row r="1076">
       <c r="A1076" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="B1076" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="C1076" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="D1076" t="s">
         <v>13</v>
@@ -41625,13 +41632,13 @@
     </row>
     <row r="1077">
       <c r="A1077" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="B1077" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="C1077" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="D1077" t="s">
         <v>13</v>
@@ -41653,13 +41660,13 @@
     </row>
     <row r="1078">
       <c r="A1078" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="B1078" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="C1078" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="D1078" t="s">
         <v>77</v>
@@ -41681,13 +41688,13 @@
     </row>
     <row r="1079">
       <c r="A1079" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="B1079" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="C1079" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="D1079" t="s">
         <v>13</v>
@@ -41709,13 +41716,13 @@
     </row>
     <row r="1080">
       <c r="A1080" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="B1080" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="C1080" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="D1080" t="s">
         <v>13</v>
@@ -41737,13 +41744,13 @@
     </row>
     <row r="1081">
       <c r="A1081" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="B1081" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="C1081" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="D1081" t="s">
         <v>13</v>
@@ -41765,13 +41772,13 @@
     </row>
     <row r="1082">
       <c r="A1082" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="B1082" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="C1082" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="D1082" t="s">
         <v>13</v>
@@ -41793,13 +41800,13 @@
     </row>
     <row r="1083">
       <c r="A1083" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="B1083" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="C1083" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="D1083" t="s">
         <v>13</v>
@@ -41821,13 +41828,13 @@
     </row>
     <row r="1084">
       <c r="A1084" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="B1084" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="C1084" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="D1084" t="s">
         <v>77</v>
@@ -41849,13 +41856,13 @@
     </row>
     <row r="1085">
       <c r="A1085" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="B1085" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="C1085" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="D1085" t="s">
         <v>13</v>
@@ -41877,13 +41884,13 @@
     </row>
     <row r="1086">
       <c r="A1086" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="B1086" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="C1086" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="D1086" t="s">
         <v>13</v>
@@ -41892,7 +41899,7 @@
         <v>100</v>
       </c>
       <c r="F1086" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1086" t="s">
         <v>26</v>
@@ -41905,13 +41912,13 @@
     </row>
     <row r="1087">
       <c r="A1087" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="B1087" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="C1087" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="D1087" t="s">
         <v>13</v>
@@ -41920,7 +41927,7 @@
         <v>100</v>
       </c>
       <c r="F1087" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1087" t="s">
         <v>26</v>
@@ -41933,13 +41940,13 @@
     </row>
     <row r="1088">
       <c r="A1088" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="B1088" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="C1088" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="D1088" t="s">
         <v>13</v>
@@ -41948,7 +41955,7 @@
         <v>100</v>
       </c>
       <c r="F1088" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1088" t="s">
         <v>26</v>
@@ -41961,13 +41968,13 @@
     </row>
     <row r="1089">
       <c r="A1089" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="B1089" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="C1089" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="D1089" t="s">
         <v>13</v>
@@ -41976,7 +41983,7 @@
         <v>100</v>
       </c>
       <c r="F1089" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1089" t="s">
         <v>26</v>
@@ -41989,13 +41996,13 @@
     </row>
     <row r="1090">
       <c r="A1090" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="B1090" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C1090" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="D1090" t="s">
         <v>13</v>
@@ -42004,7 +42011,7 @@
         <v>100</v>
       </c>
       <c r="F1090" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1090" t="s">
         <v>26</v>
@@ -42017,13 +42024,13 @@
     </row>
     <row r="1091">
       <c r="A1091" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="B1091" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="C1091" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="D1091" t="s">
         <v>13</v>
@@ -42032,7 +42039,7 @@
         <v>100</v>
       </c>
       <c r="F1091" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1091" t="s">
         <v>26</v>
@@ -42045,13 +42052,13 @@
     </row>
     <row r="1092">
       <c r="A1092" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="B1092" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="C1092" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="D1092" t="s">
         <v>13</v>
@@ -42060,7 +42067,7 @@
         <v>100</v>
       </c>
       <c r="F1092" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1092" t="s">
         <v>26</v>
@@ -42073,13 +42080,13 @@
     </row>
     <row r="1093">
       <c r="A1093" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="B1093" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="C1093" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="D1093" t="s">
         <v>13</v>
@@ -42088,7 +42095,7 @@
         <v>100</v>
       </c>
       <c r="F1093" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1093" t="s">
         <v>26</v>
@@ -42101,13 +42108,13 @@
     </row>
     <row r="1094">
       <c r="A1094" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="B1094" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="C1094" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="D1094" t="s">
         <v>13</v>
@@ -42116,7 +42123,7 @@
         <v>100</v>
       </c>
       <c r="F1094" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1094" t="s">
         <v>26</v>
@@ -42129,13 +42136,13 @@
     </row>
     <row r="1095">
       <c r="A1095" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="B1095" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="C1095" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="D1095" t="s">
         <v>13</v>
@@ -42144,7 +42151,7 @@
         <v>100</v>
       </c>
       <c r="F1095" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1095" t="s">
         <v>26</v>
@@ -42157,13 +42164,13 @@
     </row>
     <row r="1096">
       <c r="A1096" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="B1096" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="C1096" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="D1096" t="s">
         <v>13</v>
@@ -42172,7 +42179,7 @@
         <v>100</v>
       </c>
       <c r="F1096" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1096" t="s">
         <v>26</v>
@@ -42185,13 +42192,13 @@
     </row>
     <row r="1097">
       <c r="A1097" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="B1097" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="C1097" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="D1097" t="s">
         <v>13</v>
@@ -42200,7 +42207,7 @@
         <v>100</v>
       </c>
       <c r="F1097" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1097" t="s">
         <v>26</v>
@@ -42213,13 +42220,13 @@
     </row>
     <row r="1098">
       <c r="A1098" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="B1098" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="C1098" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="D1098" t="s">
         <v>13</v>
@@ -42228,7 +42235,7 @@
         <v>100</v>
       </c>
       <c r="F1098" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1098" t="s">
         <v>26</v>
@@ -42241,13 +42248,13 @@
     </row>
     <row r="1099">
       <c r="A1099" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="B1099" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="C1099" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="D1099" t="s">
         <v>13</v>
@@ -42256,7 +42263,7 @@
         <v>100</v>
       </c>
       <c r="F1099" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1099" t="s">
         <v>26</v>
@@ -42269,13 +42276,13 @@
     </row>
     <row r="1100">
       <c r="A1100" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="B1100" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="C1100" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="D1100" t="s">
         <v>13</v>
@@ -42284,7 +42291,7 @@
         <v>100</v>
       </c>
       <c r="F1100" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1100" t="s">
         <v>26</v>
@@ -42297,13 +42304,13 @@
     </row>
     <row r="1101">
       <c r="A1101" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="B1101" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C1101" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="D1101" t="s">
         <v>13</v>
@@ -42312,7 +42319,7 @@
         <v>100</v>
       </c>
       <c r="F1101" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1101" t="s">
         <v>26</v>
@@ -42325,13 +42332,13 @@
     </row>
     <row r="1102">
       <c r="A1102" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="B1102" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="C1102" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="D1102" t="s">
         <v>13</v>
@@ -42340,7 +42347,7 @@
         <v>100</v>
       </c>
       <c r="F1102" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1102" t="s">
         <v>26</v>
@@ -42353,13 +42360,13 @@
     </row>
     <row r="1103">
       <c r="A1103" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="B1103" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="C1103" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="D1103" t="s">
         <v>13</v>
@@ -42368,7 +42375,7 @@
         <v>100</v>
       </c>
       <c r="F1103" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1103" t="s">
         <v>26</v>
@@ -42381,13 +42388,13 @@
     </row>
     <row r="1104">
       <c r="A1104" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="B1104" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="C1104" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="D1104" t="s">
         <v>13</v>
@@ -42396,7 +42403,7 @@
         <v>100</v>
       </c>
       <c r="F1104" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1104" t="s">
         <v>26</v>
@@ -42409,13 +42416,13 @@
     </row>
     <row r="1105">
       <c r="A1105" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="B1105" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="C1105" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="D1105" t="s">
         <v>13</v>
@@ -42424,7 +42431,7 @@
         <v>100</v>
       </c>
       <c r="F1105" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1105" t="s">
         <v>26</v>
@@ -42437,13 +42444,13 @@
     </row>
     <row r="1106">
       <c r="A1106" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="B1106" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="C1106" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="D1106" t="s">
         <v>13</v>
@@ -42452,7 +42459,7 @@
         <v>100</v>
       </c>
       <c r="F1106" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G1106" t="s">
         <v>26</v>
@@ -42465,13 +42472,13 @@
     </row>
     <row r="1107">
       <c r="A1107" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="B1107" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="C1107" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="D1107" t="s">
         <v>13</v>
@@ -42493,13 +42500,13 @@
     </row>
     <row r="1108">
       <c r="A1108" t="s">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="B1108" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="C1108" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="D1108" t="s">
         <v>13</v>
@@ -42521,13 +42528,13 @@
     </row>
     <row r="1109">
       <c r="A1109" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="B1109" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="C1109" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="D1109" t="s">
         <v>13</v>
@@ -42549,13 +42556,13 @@
     </row>
     <row r="1110">
       <c r="A1110" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="B1110" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="C1110" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="D1110" t="s">
         <v>13</v>
@@ -42577,13 +42584,13 @@
     </row>
     <row r="1111">
       <c r="A1111" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="B1111" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="C1111" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="D1111" t="s">
         <v>13</v>
@@ -42605,13 +42612,13 @@
     </row>
     <row r="1112">
       <c r="A1112" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="B1112" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="C1112" t="s">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="D1112" t="s">
         <v>13</v>
@@ -42633,13 +42640,13 @@
     </row>
     <row r="1113">
       <c r="A1113" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="B1113" t="s">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="C1113" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="D1113" t="s">
         <v>13</v>
@@ -42661,13 +42668,13 @@
     </row>
     <row r="1114">
       <c r="A1114" t="s">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="B1114" t="s">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="C1114" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="D1114" t="s">
         <v>13</v>
@@ -42689,13 +42696,13 @@
     </row>
     <row r="1115">
       <c r="A1115" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="B1115" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="C1115" t="s">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="D1115" t="s">
         <v>13</v>
@@ -42717,13 +42724,13 @@
     </row>
     <row r="1116">
       <c r="A1116" t="s">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="B1116" t="s">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="C1116" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="D1116" t="s">
         <v>13</v>
@@ -42745,13 +42752,13 @@
     </row>
     <row r="1117">
       <c r="A1117" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="B1117" t="s">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="C1117" t="s">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="D1117" t="s">
         <v>13</v>
@@ -42773,13 +42780,13 @@
     </row>
     <row r="1118">
       <c r="A1118" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="B1118" t="s">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="C1118" t="s">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="D1118" t="s">
         <v>13</v>
@@ -42788,7 +42795,7 @@
         <v>100</v>
       </c>
       <c r="F1118" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="G1118" t="s">
         <v>69</v>
@@ -42801,13 +42808,13 @@
     </row>
     <row r="1119">
       <c r="A1119" t="s">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="B1119" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="C1119" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="D1119" t="s">
         <v>13</v>
@@ -42829,13 +42836,13 @@
     </row>
     <row r="1120">
       <c r="A1120" t="s">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="B1120" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="C1120" t="s">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="D1120" t="s">
         <v>77</v>
@@ -42857,13 +42864,13 @@
     </row>
     <row r="1121">
       <c r="A1121" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="B1121" t="s">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="C1121" t="s">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="D1121" t="s">
         <v>13</v>
@@ -42885,13 +42892,13 @@
     </row>
     <row r="1122">
       <c r="A1122" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="B1122" t="s">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="C1122" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="D1122" t="s">
         <v>13</v>
